--- a/assets/ASIENTOS_CONTABLES_DETALLE2.xlsx
+++ b/assets/ASIENTOS_CONTABLES_DETALLE2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proyecto4\OneDrive - LLAMA GAS S.A\Documentos\GitHub\Jobs_JE\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://llamgas-my.sharepoint.com/personal/analista_proyectos_grupollamagas_pe/Documents/Documentos/GitHub/Jobs_JE/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B53188C-8C66-48EB-A944-8F33A0B1AF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{8B53188C-8C66-48EB-A944-8F33A0B1AF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8E44A0-6082-40E9-8676-56064EC2AEFD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-975" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DetalleSaldosBancosFinal" sheetId="5" r:id="rId1"/>
@@ -972,7 +972,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1166,18 +1166,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1551,7 +1551,7 @@
       <c r="L1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="43" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="36" t="s">
@@ -1585,16 +1585,16 @@
         <v>205</v>
       </c>
       <c r="F2" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G2" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H2" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I2" s="42"/>
-      <c r="M2" s="46" t="s">
+      <c r="M2" s="44" t="s">
         <v>128</v>
       </c>
       <c r="N2" s="40"/>
@@ -1620,16 +1620,16 @@
         <v>205</v>
       </c>
       <c r="F3" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G3" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H3" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I3" s="42"/>
-      <c r="M3" s="46" t="s">
+      <c r="M3" s="44" t="s">
         <v>129</v>
       </c>
       <c r="N3" s="40"/>
@@ -1655,16 +1655,16 @@
         <v>205</v>
       </c>
       <c r="F4" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G4" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H4" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I4" s="42"/>
-      <c r="M4" s="46" t="s">
+      <c r="M4" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N4" s="40"/>
@@ -1690,16 +1690,16 @@
         <v>205</v>
       </c>
       <c r="F5" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G5" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H5" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I5" s="42"/>
-      <c r="M5" s="46" t="s">
+      <c r="M5" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N5" s="40"/>
@@ -1725,16 +1725,16 @@
         <v>205</v>
       </c>
       <c r="F6" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G6" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H6" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I6" s="42"/>
-      <c r="M6" s="46" t="s">
+      <c r="M6" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N6" s="40"/>
@@ -1760,16 +1760,16 @@
         <v>205</v>
       </c>
       <c r="F7" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G7" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H7" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I7" s="42"/>
-      <c r="M7" s="46" t="s">
+      <c r="M7" s="44" t="s">
         <v>120</v>
       </c>
       <c r="N7" s="40"/>
@@ -1795,16 +1795,16 @@
         <v>205</v>
       </c>
       <c r="F8" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G8" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H8" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I8" s="42"/>
-      <c r="M8" s="46" t="s">
+      <c r="M8" s="44" t="s">
         <v>130</v>
       </c>
       <c r="N8" s="40"/>
@@ -1830,16 +1830,16 @@
         <v>205</v>
       </c>
       <c r="F9" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G9" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H9" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I9" s="42"/>
-      <c r="M9" s="46" t="s">
+      <c r="M9" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N9" s="40"/>
@@ -1865,16 +1865,16 @@
         <v>205</v>
       </c>
       <c r="F10" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G10" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H10" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I10" s="42"/>
-      <c r="M10" s="46" t="s">
+      <c r="M10" s="44" t="s">
         <v>119</v>
       </c>
       <c r="N10" s="40"/>
@@ -1900,16 +1900,16 @@
         <v>205</v>
       </c>
       <c r="F11" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G11" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H11" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I11" s="42"/>
-      <c r="M11" s="46" t="s">
+      <c r="M11" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N11" s="40"/>
@@ -1935,16 +1935,16 @@
         <v>205</v>
       </c>
       <c r="F12" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G12" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H12" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I12" s="42"/>
-      <c r="M12" s="46" t="s">
+      <c r="M12" s="44" t="s">
         <v>119</v>
       </c>
       <c r="N12" s="40"/>
@@ -1970,16 +1970,16 @@
         <v>205</v>
       </c>
       <c r="F13" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G13" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H13" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I13" s="42"/>
-      <c r="M13" s="46" t="s">
+      <c r="M13" s="44" t="s">
         <v>131</v>
       </c>
       <c r="N13" s="40"/>
@@ -2005,16 +2005,16 @@
         <v>205</v>
       </c>
       <c r="F14" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G14" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H14" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I14" s="42"/>
-      <c r="M14" s="46" t="s">
+      <c r="M14" s="44" t="s">
         <v>116</v>
       </c>
       <c r="N14" s="40"/>
@@ -2040,16 +2040,16 @@
         <v>205</v>
       </c>
       <c r="F15" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G15" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H15" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I15" s="42"/>
-      <c r="M15" s="46" t="s">
+      <c r="M15" s="44" t="s">
         <v>118</v>
       </c>
       <c r="N15" s="40"/>
@@ -2075,18 +2075,18 @@
         <v>205</v>
       </c>
       <c r="F16" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G16" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H16" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I16" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="M16" s="46" t="s">
+      <c r="M16" s="44" t="s">
         <v>132</v>
       </c>
       <c r="N16" s="40"/>
@@ -2112,18 +2112,18 @@
         <v>205</v>
       </c>
       <c r="F17" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G17" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H17" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I17" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="M17" s="46" t="s">
+      <c r="M17" s="44" t="s">
         <v>133</v>
       </c>
       <c r="N17" s="40"/>
@@ -2149,18 +2149,18 @@
         <v>205</v>
       </c>
       <c r="F18" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G18" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H18" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I18" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="M18" s="46" t="s">
+      <c r="M18" s="44" t="s">
         <v>122</v>
       </c>
       <c r="N18" s="40"/>
@@ -2186,18 +2186,18 @@
         <v>205</v>
       </c>
       <c r="F19" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G19" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H19" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I19" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="M19" s="46" t="s">
+      <c r="M19" s="44" t="s">
         <v>121</v>
       </c>
       <c r="N19" s="40"/>
@@ -2223,16 +2223,16 @@
         <v>205</v>
       </c>
       <c r="F20" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G20" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H20" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I20" s="42"/>
-      <c r="M20" s="46" t="s">
+      <c r="M20" s="44" t="s">
         <v>134</v>
       </c>
       <c r="N20" s="40"/>
@@ -2258,16 +2258,16 @@
         <v>205</v>
       </c>
       <c r="F21" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G21" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H21" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I21" s="42"/>
-      <c r="M21" s="46" t="s">
+      <c r="M21" s="44" t="s">
         <v>135</v>
       </c>
       <c r="N21" s="40"/>
@@ -2293,16 +2293,16 @@
         <v>205</v>
       </c>
       <c r="F22" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G22" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H22" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I22" s="42"/>
-      <c r="M22" s="46" t="s">
+      <c r="M22" s="44" t="s">
         <v>136</v>
       </c>
       <c r="N22" s="40"/>
@@ -2328,16 +2328,16 @@
         <v>205</v>
       </c>
       <c r="F23" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G23" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H23" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I23" s="42"/>
-      <c r="M23" s="46" t="s">
+      <c r="M23" s="44" t="s">
         <v>126</v>
       </c>
       <c r="N23" s="40"/>
@@ -2363,16 +2363,16 @@
         <v>205</v>
       </c>
       <c r="F24" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G24" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H24" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I24" s="42"/>
-      <c r="M24" s="46" t="s">
+      <c r="M24" s="44" t="s">
         <v>137</v>
       </c>
       <c r="N24" s="40"/>
@@ -2398,16 +2398,16 @@
         <v>205</v>
       </c>
       <c r="F25" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G25" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H25" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I25" s="42"/>
-      <c r="M25" s="46" t="s">
+      <c r="M25" s="44" t="s">
         <v>138</v>
       </c>
       <c r="N25" s="40"/>
@@ -2433,16 +2433,16 @@
         <v>205</v>
       </c>
       <c r="F26" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G26" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H26" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I26" s="42"/>
-      <c r="M26" s="46" t="s">
+      <c r="M26" s="44" t="s">
         <v>139</v>
       </c>
       <c r="N26" s="40"/>
@@ -2468,18 +2468,18 @@
         <v>205</v>
       </c>
       <c r="F27" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G27" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H27" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I27" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="M27" s="46" t="s">
+      <c r="M27" s="44" t="s">
         <v>117</v>
       </c>
       <c r="N27" s="40"/>
@@ -2505,18 +2505,18 @@
         <v>205</v>
       </c>
       <c r="F28" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G28" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H28" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I28" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="M28" s="46" t="s">
+      <c r="M28" s="44" t="s">
         <v>117</v>
       </c>
       <c r="N28" s="40"/>
@@ -2542,18 +2542,18 @@
         <v>205</v>
       </c>
       <c r="F29" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G29" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H29" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I29" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="M29" s="46" t="s">
+      <c r="M29" s="44" t="s">
         <v>122</v>
       </c>
       <c r="N29" s="40"/>
@@ -2579,18 +2579,18 @@
         <v>205</v>
       </c>
       <c r="F30" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G30" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H30" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I30" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="M30" s="46" t="s">
+      <c r="M30" s="44" t="s">
         <v>115</v>
       </c>
       <c r="N30" s="40"/>
@@ -2616,18 +2616,18 @@
         <v>205</v>
       </c>
       <c r="F31" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G31" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H31" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I31" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="M31" s="46" t="s">
+      <c r="M31" s="44" t="s">
         <v>122</v>
       </c>
       <c r="N31" s="40"/>
@@ -2653,18 +2653,18 @@
         <v>205</v>
       </c>
       <c r="F32" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G32" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H32" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I32" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="M32" s="46" t="s">
+      <c r="M32" s="44" t="s">
         <v>140</v>
       </c>
       <c r="N32" s="40"/>
@@ -2690,18 +2690,18 @@
         <v>205</v>
       </c>
       <c r="F33" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G33" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H33" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I33" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="M33" s="46" t="s">
+      <c r="M33" s="44" t="s">
         <v>141</v>
       </c>
       <c r="N33" s="40"/>
@@ -2727,18 +2727,18 @@
         <v>205</v>
       </c>
       <c r="F34" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G34" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H34" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I34" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="M34" s="46" t="s">
+      <c r="M34" s="44" t="s">
         <v>142</v>
       </c>
       <c r="N34" s="40"/>
@@ -2764,18 +2764,18 @@
         <v>205</v>
       </c>
       <c r="F35" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G35" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H35" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I35" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="M35" s="46" t="s">
+      <c r="M35" s="44" t="s">
         <v>143</v>
       </c>
       <c r="N35" s="40"/>
@@ -2801,18 +2801,18 @@
         <v>205</v>
       </c>
       <c r="F36" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G36" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H36" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I36" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="M36" s="46" t="s">
+      <c r="M36" s="44" t="s">
         <v>144</v>
       </c>
       <c r="N36" s="40"/>
@@ -2838,18 +2838,18 @@
         <v>205</v>
       </c>
       <c r="F37" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G37" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H37" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I37" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="M37" s="46" t="s">
+      <c r="M37" s="44" t="s">
         <v>145</v>
       </c>
       <c r="N37" s="40"/>
@@ -2875,18 +2875,18 @@
         <v>205</v>
       </c>
       <c r="F38" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G38" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H38" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I38" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="M38" s="46" t="s">
+      <c r="M38" s="44" t="s">
         <v>127</v>
       </c>
       <c r="N38" s="40"/>
@@ -2912,18 +2912,18 @@
         <v>205</v>
       </c>
       <c r="F39" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G39" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H39" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I39" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="M39" s="47" t="s">
+      <c r="M39" s="45" t="s">
         <v>152</v>
       </c>
       <c r="N39" s="40"/>
@@ -2949,18 +2949,18 @@
         <v>205</v>
       </c>
       <c r="F40" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G40" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H40" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I40" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="M40" s="47" t="s">
+      <c r="M40" s="45" t="s">
         <v>153</v>
       </c>
       <c r="N40" s="40"/>
@@ -2986,18 +2986,18 @@
         <v>205</v>
       </c>
       <c r="F41" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G41" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H41" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I41" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="M41" s="47" t="s">
+      <c r="M41" s="45" t="s">
         <v>154</v>
       </c>
       <c r="N41" s="40"/>
@@ -3023,18 +3023,18 @@
         <v>205</v>
       </c>
       <c r="F42" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G42" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H42" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I42" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="M42" s="47" t="s">
+      <c r="M42" s="45" t="s">
         <v>155</v>
       </c>
       <c r="N42" s="40"/>
@@ -3060,18 +3060,18 @@
         <v>205</v>
       </c>
       <c r="F43" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G43" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H43" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I43" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="M43" s="47" t="s">
+      <c r="M43" s="45" t="s">
         <v>156</v>
       </c>
       <c r="N43" s="40"/>
@@ -3097,18 +3097,18 @@
         <v>205</v>
       </c>
       <c r="F44" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G44" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H44" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I44" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="M44" s="47" t="s">
+      <c r="M44" s="45" t="s">
         <v>157</v>
       </c>
       <c r="N44" s="40"/>
@@ -3134,18 +3134,18 @@
         <v>205</v>
       </c>
       <c r="F45" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G45" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H45" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I45" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="M45" s="47" t="s">
+      <c r="M45" s="45" t="s">
         <v>158</v>
       </c>
       <c r="N45" s="40"/>
@@ -3171,18 +3171,18 @@
         <v>205</v>
       </c>
       <c r="F46" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G46" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H46" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I46" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="M46" s="47" t="s">
+      <c r="M46" s="45" t="s">
         <v>159</v>
       </c>
       <c r="N46" s="40"/>
@@ -3208,18 +3208,18 @@
         <v>205</v>
       </c>
       <c r="F47" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G47" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H47" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I47" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="M47" s="47" t="s">
+      <c r="M47" s="45" t="s">
         <v>160</v>
       </c>
       <c r="N47" s="40"/>
@@ -3245,18 +3245,18 @@
         <v>205</v>
       </c>
       <c r="F48" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G48" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H48" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I48" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="M48" s="47" t="s">
+      <c r="M48" s="45" t="s">
         <v>161</v>
       </c>
       <c r="N48" s="40"/>
@@ -3282,18 +3282,18 @@
         <v>205</v>
       </c>
       <c r="F49" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G49" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H49" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I49" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="M49" s="47" t="s">
+      <c r="M49" s="45" t="s">
         <v>125</v>
       </c>
       <c r="N49" s="40"/>
@@ -3319,18 +3319,18 @@
         <v>205</v>
       </c>
       <c r="F50" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G50" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H50" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I50" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="M50" s="47" t="s">
+      <c r="M50" s="45" t="s">
         <v>162</v>
       </c>
       <c r="N50" s="40"/>
@@ -3356,18 +3356,18 @@
         <v>205</v>
       </c>
       <c r="F51" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G51" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H51" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I51" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="M51" s="47" t="s">
+      <c r="M51" s="45" t="s">
         <v>124</v>
       </c>
       <c r="N51" s="40"/>
@@ -3393,18 +3393,18 @@
         <v>205</v>
       </c>
       <c r="F52" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G52" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H52" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I52" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="M52" s="47" t="s">
+      <c r="M52" s="45" t="s">
         <v>163</v>
       </c>
       <c r="N52" s="40"/>
@@ -3430,18 +3430,18 @@
         <v>205</v>
       </c>
       <c r="F53" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G53" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H53" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I53" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="M53" s="47" t="s">
+      <c r="M53" s="45" t="s">
         <v>164</v>
       </c>
       <c r="N53" s="40"/>
@@ -3467,18 +3467,18 @@
         <v>205</v>
       </c>
       <c r="F54" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G54" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H54" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I54" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="M54" s="47" t="s">
+      <c r="M54" s="45" t="s">
         <v>151</v>
       </c>
       <c r="N54" s="40"/>
@@ -3504,18 +3504,18 @@
         <v>205</v>
       </c>
       <c r="F55" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G55" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H55" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I55" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="M55" s="47" t="s">
+      <c r="M55" s="45" t="s">
         <v>150</v>
       </c>
       <c r="N55" s="40"/>
@@ -3541,18 +3541,18 @@
         <v>205</v>
       </c>
       <c r="F56" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G56" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H56" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I56" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="M56" s="47" t="s">
+      <c r="M56" s="45" t="s">
         <v>165</v>
       </c>
       <c r="N56" s="40"/>
@@ -3578,18 +3578,18 @@
         <v>205</v>
       </c>
       <c r="F57" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G57" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H57" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I57" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="M57" s="47" t="s">
+      <c r="M57" s="45" t="s">
         <v>166</v>
       </c>
       <c r="N57" s="40"/>
@@ -3615,18 +3615,18 @@
         <v>205</v>
       </c>
       <c r="F58" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G58" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H58" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I58" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="M58" s="47" t="s">
+      <c r="M58" s="45" t="s">
         <v>167</v>
       </c>
       <c r="N58" s="40"/>
@@ -3652,18 +3652,18 @@
         <v>205</v>
       </c>
       <c r="F59" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G59" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H59" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I59" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="M59" s="47" t="s">
+      <c r="M59" s="45" t="s">
         <v>168</v>
       </c>
       <c r="N59" s="40"/>
@@ -3689,18 +3689,18 @@
         <v>205</v>
       </c>
       <c r="F60" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G60" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H60" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I60" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="M60" s="47" t="s">
+      <c r="M60" s="45" t="s">
         <v>169</v>
       </c>
       <c r="N60" s="40"/>
@@ -3726,18 +3726,18 @@
         <v>205</v>
       </c>
       <c r="F61" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G61" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H61" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I61" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="M61" s="47" t="s">
+      <c r="M61" s="45" t="s">
         <v>170</v>
       </c>
       <c r="N61" s="40"/>
@@ -3763,18 +3763,18 @@
         <v>205</v>
       </c>
       <c r="F62" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G62" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H62" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I62" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="M62" s="47" t="s">
+      <c r="M62" s="45" t="s">
         <v>171</v>
       </c>
       <c r="N62" s="40"/>
@@ -3800,18 +3800,18 @@
         <v>205</v>
       </c>
       <c r="F63" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G63" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H63" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I63" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="M63" s="47" t="s">
+      <c r="M63" s="45" t="s">
         <v>172</v>
       </c>
       <c r="N63" s="40"/>
@@ -3837,18 +3837,18 @@
         <v>205</v>
       </c>
       <c r="F64" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G64" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H64" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I64" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="M64" s="47" t="s">
+      <c r="M64" s="45" t="s">
         <v>173</v>
       </c>
       <c r="N64" s="40"/>
@@ -3874,18 +3874,18 @@
         <v>205</v>
       </c>
       <c r="F65" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G65" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H65" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I65" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="M65" s="47" t="s">
+      <c r="M65" s="45" t="s">
         <v>174</v>
       </c>
       <c r="N65" s="40"/>
@@ -3911,18 +3911,18 @@
         <v>205</v>
       </c>
       <c r="F66" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G66" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H66" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I66" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="M66" s="47" t="s">
+      <c r="M66" s="45" t="s">
         <v>147</v>
       </c>
       <c r="N66" s="40"/>
@@ -3948,18 +3948,18 @@
         <v>205</v>
       </c>
       <c r="F67" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G67" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H67" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I67" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="M67" s="47" t="s">
+      <c r="M67" s="45" t="s">
         <v>175</v>
       </c>
       <c r="N67" s="40"/>
@@ -3985,18 +3985,18 @@
         <v>205</v>
       </c>
       <c r="F68" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G68" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H68" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I68" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="M68" s="47" t="s">
+      <c r="M68" s="45" t="s">
         <v>124</v>
       </c>
       <c r="N68" s="40"/>
@@ -4022,18 +4022,18 @@
         <v>205</v>
       </c>
       <c r="F69" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G69" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H69" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I69" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="M69" s="47" t="s">
+      <c r="M69" s="45" t="s">
         <v>176</v>
       </c>
       <c r="N69" s="40"/>
@@ -4059,18 +4059,18 @@
         <v>205</v>
       </c>
       <c r="F70" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G70" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H70" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I70" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="M70" s="47" t="s">
+      <c r="M70" s="45" t="s">
         <v>177</v>
       </c>
       <c r="N70" s="40"/>
@@ -4096,18 +4096,18 @@
         <v>205</v>
       </c>
       <c r="F71" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G71" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H71" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I71" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="M71" s="47" t="s">
+      <c r="M71" s="45" t="s">
         <v>178</v>
       </c>
       <c r="N71" s="40"/>
@@ -4133,18 +4133,18 @@
         <v>205</v>
       </c>
       <c r="F72" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G72" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H72" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I72" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="M72" s="47" t="s">
+      <c r="M72" s="45" t="s">
         <v>179</v>
       </c>
       <c r="N72" s="40"/>
@@ -4170,18 +4170,18 @@
         <v>205</v>
       </c>
       <c r="F73" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G73" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H73" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I73" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="M73" s="47" t="s">
+      <c r="M73" s="45" t="s">
         <v>180</v>
       </c>
       <c r="N73" s="40"/>
@@ -4207,18 +4207,18 @@
         <v>205</v>
       </c>
       <c r="F74" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G74" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H74" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I74" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="M74" s="47" t="s">
+      <c r="M74" s="45" t="s">
         <v>181</v>
       </c>
       <c r="N74" s="40"/>
@@ -4244,18 +4244,18 @@
         <v>205</v>
       </c>
       <c r="F75" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G75" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H75" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I75" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="M75" s="47" t="s">
+      <c r="M75" s="45" t="s">
         <v>182</v>
       </c>
       <c r="N75" s="40"/>
@@ -4281,18 +4281,18 @@
         <v>205</v>
       </c>
       <c r="F76" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G76" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H76" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I76" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="M76" s="47" t="s">
+      <c r="M76" s="45" t="s">
         <v>183</v>
       </c>
       <c r="N76" s="40"/>
@@ -4318,18 +4318,18 @@
         <v>205</v>
       </c>
       <c r="F77" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G77" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H77" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I77" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="M77" s="47" t="s">
+      <c r="M77" s="45" t="s">
         <v>184</v>
       </c>
       <c r="N77" s="40"/>
@@ -4355,18 +4355,18 @@
         <v>205</v>
       </c>
       <c r="F78" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G78" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H78" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I78" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="M78" s="47" t="s">
+      <c r="M78" s="45" t="s">
         <v>185</v>
       </c>
       <c r="N78" s="40"/>
@@ -4392,18 +4392,18 @@
         <v>205</v>
       </c>
       <c r="F79" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G79" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H79" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I79" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="M79" s="47" t="s">
+      <c r="M79" s="45" t="s">
         <v>186</v>
       </c>
       <c r="N79" s="40"/>
@@ -4429,18 +4429,18 @@
         <v>205</v>
       </c>
       <c r="F80" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G80" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H80" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I80" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="M80" s="47" t="s">
+      <c r="M80" s="45" t="s">
         <v>187</v>
       </c>
       <c r="N80" s="40"/>
@@ -4466,18 +4466,18 @@
         <v>205</v>
       </c>
       <c r="F81" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G81" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H81" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I81" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="M81" s="47" t="s">
+      <c r="M81" s="45" t="s">
         <v>188</v>
       </c>
       <c r="N81" s="40"/>
@@ -4503,18 +4503,18 @@
         <v>205</v>
       </c>
       <c r="F82" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G82" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H82" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I82" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="M82" s="47" t="s">
+      <c r="M82" s="45" t="s">
         <v>189</v>
       </c>
       <c r="N82" s="40"/>
@@ -4540,18 +4540,18 @@
         <v>205</v>
       </c>
       <c r="F83" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G83" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H83" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I83" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="M83" s="47"/>
+      <c r="M83" s="45"/>
       <c r="N83" s="40">
         <v>8</v>
       </c>
@@ -4577,18 +4577,18 @@
         <v>205</v>
       </c>
       <c r="F84" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G84" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H84" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I84" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="M84" s="47" t="s">
+      <c r="M84" s="45" t="s">
         <v>190</v>
       </c>
       <c r="N84" s="40"/>
@@ -4614,18 +4614,18 @@
         <v>205</v>
       </c>
       <c r="F85" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G85" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H85" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I85" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="M85" s="47" t="s">
+      <c r="M85" s="45" t="s">
         <v>191</v>
       </c>
       <c r="N85" s="40"/>
@@ -4651,18 +4651,18 @@
         <v>205</v>
       </c>
       <c r="F86" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G86" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H86" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I86" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="M86" s="47" t="s">
+      <c r="M86" s="45" t="s">
         <v>192</v>
       </c>
       <c r="N86" s="40"/>
@@ -4688,18 +4688,18 @@
         <v>205</v>
       </c>
       <c r="F87" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G87" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H87" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I87" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="M87" s="47" t="s">
+      <c r="M87" s="45" t="s">
         <v>193</v>
       </c>
       <c r="N87" s="40"/>
@@ -4725,18 +4725,18 @@
         <v>205</v>
       </c>
       <c r="F88" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G88" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H88" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I88" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="M88" s="47" t="s">
+      <c r="M88" s="45" t="s">
         <v>194</v>
       </c>
       <c r="N88" s="40"/>
@@ -4762,18 +4762,18 @@
         <v>205</v>
       </c>
       <c r="F89" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G89" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H89" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I89" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="M89" s="47" t="s">
+      <c r="M89" s="45" t="s">
         <v>195</v>
       </c>
       <c r="N89" s="40"/>
@@ -4799,18 +4799,18 @@
         <v>205</v>
       </c>
       <c r="F90" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G90" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H90" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I90" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="M90" s="47" t="s">
+      <c r="M90" s="45" t="s">
         <v>196</v>
       </c>
       <c r="N90" s="40"/>
@@ -4836,18 +4836,18 @@
         <v>205</v>
       </c>
       <c r="F91" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G91" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H91" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I91" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="M91" s="47" t="s">
+      <c r="M91" s="45" t="s">
         <v>149</v>
       </c>
       <c r="N91" s="40"/>
@@ -4873,18 +4873,18 @@
         <v>205</v>
       </c>
       <c r="F92" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G92" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H92" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I92" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="M92" s="47" t="s">
+      <c r="M92" s="45" t="s">
         <v>197</v>
       </c>
       <c r="N92" s="40"/>
@@ -4910,18 +4910,18 @@
         <v>205</v>
       </c>
       <c r="F93" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G93" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H93" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I93" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="M93" s="47" t="s">
+      <c r="M93" s="45" t="s">
         <v>148</v>
       </c>
       <c r="N93" s="40"/>
@@ -4947,18 +4947,18 @@
         <v>205</v>
       </c>
       <c r="F94" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G94" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H94" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I94" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="M94" s="47" t="s">
+      <c r="M94" s="45" t="s">
         <v>198</v>
       </c>
       <c r="N94" s="40"/>
@@ -4984,18 +4984,18 @@
         <v>205</v>
       </c>
       <c r="F95" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G95" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H95" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I95" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="M95" s="47" t="s">
+      <c r="M95" s="45" t="s">
         <v>199</v>
       </c>
       <c r="N95" s="40"/>
@@ -5021,18 +5021,18 @@
         <v>205</v>
       </c>
       <c r="F96" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G96" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H96" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I96" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="M96" s="47" t="s">
+      <c r="M96" s="45" t="s">
         <v>200</v>
       </c>
       <c r="N96" s="40"/>
@@ -5058,18 +5058,18 @@
         <v>205</v>
       </c>
       <c r="F97" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G97" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H97" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I97" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="M97" s="47" t="s">
+      <c r="M97" s="45" t="s">
         <v>158</v>
       </c>
       <c r="N97" s="40"/>
@@ -5095,18 +5095,18 @@
         <v>205</v>
       </c>
       <c r="F98" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G98" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H98" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I98" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="M98" s="47" t="s">
+      <c r="M98" s="45" t="s">
         <v>201</v>
       </c>
       <c r="N98" s="40"/>
@@ -5132,18 +5132,18 @@
         <v>205</v>
       </c>
       <c r="F99" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G99" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H99" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I99" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="M99" s="47"/>
+      <c r="M99" s="45"/>
       <c r="N99" s="4">
         <v>33030.839999999997</v>
       </c>
@@ -5169,18 +5169,18 @@
         <v>205</v>
       </c>
       <c r="F100" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G100" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H100" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I100" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="M100" s="47" t="s">
+      <c r="M100" s="45" t="s">
         <v>146</v>
       </c>
       <c r="N100" s="40"/>
@@ -5206,18 +5206,18 @@
         <v>205</v>
       </c>
       <c r="F101" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G101" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H101" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I101" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="M101" s="47" t="s">
+      <c r="M101" s="45" t="s">
         <v>202</v>
       </c>
       <c r="N101" s="40"/>
@@ -5243,18 +5243,18 @@
         <v>205</v>
       </c>
       <c r="F102" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G102" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H102" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I102" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="M102" s="47" t="s">
+      <c r="M102" s="45" t="s">
         <v>124</v>
       </c>
       <c r="N102" s="40"/>
@@ -5280,18 +5280,18 @@
         <v>205</v>
       </c>
       <c r="F103" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G103" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H103" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I103" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="M103" s="47" t="s">
+      <c r="M103" s="45" t="s">
         <v>197</v>
       </c>
       <c r="N103" s="40"/>
@@ -5317,18 +5317,18 @@
         <v>205</v>
       </c>
       <c r="F104" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G104" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H104" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I104" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="M104" s="47" t="s">
+      <c r="M104" s="45" t="s">
         <v>123</v>
       </c>
       <c r="N104" s="40"/>
@@ -5354,18 +5354,18 @@
         <v>205</v>
       </c>
       <c r="F105" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G105" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H105" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I105" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="M105" s="47" t="s">
+      <c r="M105" s="45" t="s">
         <v>203</v>
       </c>
       <c r="N105" s="40"/>
@@ -5391,18 +5391,18 @@
         <v>205</v>
       </c>
       <c r="F106" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="G106" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="H106" s="2">
-        <v>20250731</v>
+        <v>20260319</v>
       </c>
       <c r="I106" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="M106" s="47" t="s">
+      <c r="M106" s="45" t="s">
         <v>204</v>
       </c>
       <c r="N106" s="40"/>
@@ -6412,22 +6412,22 @@
         <v>70</v>
       </c>
       <c r="C1" s="13"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="44"/>
+      <c r="E1" s="47"/>
       <c r="F1" s="21" t="s">
         <v>72</v>
       </c>
       <c r="G1" s="22"/>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="44"/>
-      <c r="J1" s="43" t="s">
+      <c r="I1" s="47"/>
+      <c r="J1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="44"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="13" t="s">
